--- a/data/excel/questcfg.xlsx
+++ b/data/excel/questcfg.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="66">
   <si>
     <t>CfgId</t>
   </si>
@@ -47,7 +47,7 @@
   </si>
   <si>
     <t>Rewards
-#Field=full#Ref=ItemCfg</t>
+#Field=full#Ref=ItemCfg#Merge</t>
   </si>
   <si>
     <t>NextQuests</t>
@@ -108,7 +108,10 @@
     <t>3_5</t>
   </si>
   <si>
-    <t>CfgId_1#Num_5;CfgId_3#Num_1</t>
+    <t>CfgId_1#Num_5</t>
+  </si>
+  <si>
+    <t>CfgId_3#Num_1</t>
   </si>
   <si>
     <t>5场PVP示例,演示同一个进度类型使用动态属性而编辑出新的任务</t>
@@ -123,7 +126,7 @@
     <t>4_5</t>
   </si>
   <si>
-    <t>CfgId_1#Num_5;CfgId_4#Num_2</t>
+    <t>CfgId_4#Num_2</t>
   </si>
   <si>
     <t>赢5场PVP示例,演示同一个进度类型使用动态属性而编辑出新的任务</t>
@@ -135,8 +138,10 @@
     <t>5_5</t>
   </si>
   <si>
-    <t>CfgId_1#Num_5
-CfgId_2#Num_1;CfgId_4#Num_3</t>
+    <t>CfgId_4#Num_3</t>
+  </si>
+  <si>
+    <t>CfgId_2#Num_1</t>
   </si>
   <si>
     <t>赢5场指定条件的PVP,演示复杂的数值比较接口</t>
@@ -197,9 +202,6 @@
   </si>
   <si>
     <t>7_5</t>
-  </si>
-  <si>
-    <t>CfgId_1#Num_5</t>
   </si>
   <si>
     <t>活动4子任务:在线5分钟</t>
@@ -842,9 +844,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1382,7 +1387,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.375" customWidth="1"/>
@@ -1391,12 +1396,13 @@
     <col min="4" max="4" width="18.625" customWidth="1"/>
     <col min="5" max="5" width="17.125" customWidth="1"/>
     <col min="6" max="6" width="30.375" customWidth="1"/>
-    <col min="7" max="7" width="11.5" customWidth="1"/>
-    <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="62.25" customWidth="1"/>
+    <col min="7" max="8" width="29.625" customWidth="1"/>
+    <col min="9" max="9" width="11.5" customWidth="1"/>
+    <col min="10" max="10" width="19" customWidth="1"/>
+    <col min="11" max="11" width="62.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1" spans="1:9">
+    <row r="1" ht="32" customHeight="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1415,17 +1421,23 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="60" customHeight="1" spans="1:9">
+    <row r="2" ht="60" customHeight="1" spans="1:11">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1451,10 +1463,16 @@
         <v>9</v>
       </c>
       <c r="I2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1" spans="1:6">
+    <row r="3" ht="60" customHeight="1" spans="1:11">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1468,7 +1486,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1484,12 +1502,12 @@
       <c r="F4" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="1"/>
-      <c r="I4" t="s">
+      <c r="J4" s="1"/>
+      <c r="K4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>2</v>
       </c>
@@ -1505,11 +1523,11 @@
       <c r="F5" t="s">
         <v>21</v>
       </c>
-      <c r="I5" t="s">
+      <c r="K5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>3</v>
       </c>
@@ -1525,269 +1543,281 @@
       <c r="F6" t="s">
         <v>25</v>
       </c>
-      <c r="I6" t="s">
+      <c r="G6" t="s">
         <v>26</v>
       </c>
+      <c r="K6" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" t="s">
         <v>31</v>
       </c>
+      <c r="K7" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="8" ht="27" spans="1:9">
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" t="s">
         <v>35</v>
       </c>
+      <c r="H8" t="s">
+        <v>36</v>
+      </c>
+      <c r="K8" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:11">
       <c r="A9">
         <v>20001</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F9" t="s">
         <v>17</v>
       </c>
-      <c r="I9" t="s">
-        <v>38</v>
+      <c r="K9" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:11">
       <c r="A10">
         <v>30001</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E10" t="s">
         <v>24</v>
       </c>
       <c r="F10" t="s">
-        <v>41</v>
-      </c>
-      <c r="I10" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="K10" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:11">
       <c r="A11">
         <v>30002</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F11" t="s">
         <v>17</v>
       </c>
-      <c r="I11" t="s">
-        <v>45</v>
+      <c r="K11" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:11">
       <c r="A12">
         <v>30003</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F12" t="s">
-        <v>48</v>
-      </c>
-      <c r="I12" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="K12" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:11">
       <c r="A13">
         <v>40001</v>
       </c>
       <c r="B13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F13" t="s">
-        <v>41</v>
-      </c>
-      <c r="G13">
+        <v>43</v>
+      </c>
+      <c r="I13">
         <v>40002</v>
       </c>
-      <c r="I13" t="s">
-        <v>52</v>
+      <c r="K13" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:11">
       <c r="A14">
         <v>40002</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F14" t="s">
-        <v>55</v>
-      </c>
-      <c r="G14">
+        <v>25</v>
+      </c>
+      <c r="I14">
         <v>40003</v>
       </c>
-      <c r="I14" t="s">
-        <v>56</v>
+      <c r="K14" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:11">
       <c r="A15">
         <v>40003</v>
       </c>
       <c r="B15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F15" t="s">
-        <v>59</v>
-      </c>
-      <c r="I15" t="s">
         <v>60</v>
       </c>
+      <c r="K15" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:11">
       <c r="A16">
         <v>60001</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F16" t="s">
-        <v>41</v>
-      </c>
-      <c r="I16" t="s">
-        <v>61</v>
+        <v>43</v>
+      </c>
+      <c r="K16" t="s">
+        <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:11">
       <c r="A17">
         <v>60002</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F17" t="s">
-        <v>55</v>
-      </c>
-      <c r="I17" t="s">
-        <v>62</v>
+        <v>25</v>
+      </c>
+      <c r="K17" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:11">
       <c r="A18">
         <v>60003</v>
       </c>
       <c r="B18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F18" t="s">
+        <v>65</v>
+      </c>
+      <c r="K18" t="s">
         <v>64</v>
-      </c>
-      <c r="I18" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>
